--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136880906</v>
+        <v>137150442</v>
       </c>
       <c r="B3" t="n">
-        <v>56937</v>
+        <v>58872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,50 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bokskog på blocklik terräng, Sk</t>
+          <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403050</v>
+        <v>403063</v>
       </c>
       <c r="R3" t="n">
-        <v>6212964</v>
+        <v>6212983</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,14 +868,19 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>försvann in under en sten</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,14 +903,251 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150442</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136880906</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56937</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bokskog på blocklik terräng, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>403050</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6212964</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>försvann in under en sten</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136880906</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137150433</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>403298</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6213074</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150433</t>
         </is>
       </c>
     </row>
@@ -927,6 +1155,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880893</v>
       </c>
       <c r="B2" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137150442</v>
       </c>
       <c r="B3" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136880906</v>
       </c>
       <c r="B4" t="n">
-        <v>56937</v>
+        <v>56950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137150433</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880893</v>
       </c>
       <c r="B2" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137150442</v>
       </c>
       <c r="B3" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136880906</v>
       </c>
       <c r="B4" t="n">
-        <v>56950</v>
+        <v>56952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137150433</v>
       </c>
       <c r="B5" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -714,11 +714,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -948,11 +944,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880893</v>
       </c>
       <c r="B2" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137150442</v>
       </c>
       <c r="B3" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136880906</v>
       </c>
       <c r="B4" t="n">
-        <v>56952</v>
+        <v>56962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137150433</v>
       </c>
       <c r="B5" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880893</v>
       </c>
       <c r="B2" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137150442</v>
       </c>
       <c r="B3" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136880906</v>
       </c>
       <c r="B4" t="n">
-        <v>56962</v>
+        <v>56963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137150433</v>
       </c>
       <c r="B5" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136880893</v>
       </c>
       <c r="B2" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137150442</v>
       </c>
       <c r="B3" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137150433</v>
       </c>
       <c r="B5" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136880893</v>
+        <v>137495322</v>
       </c>
       <c r="B2" t="n">
-        <v>58903</v>
+        <v>106622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>221157</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bokskog på blocklik terräng, Sk</t>
+          <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403050</v>
+        <v>402872</v>
       </c>
       <c r="R2" t="n">
-        <v>6212964</v>
+        <v>6213052</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,9 +769,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ädellövsumpskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -783,23 +788,19 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880893</t>
+          <t>https://artportalen.se/Sighting/137495322</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137150442</v>
+        <v>137495320</v>
       </c>
       <c r="B3" t="n">
-        <v>58903</v>
+        <v>98296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403063</v>
+        <v>402881</v>
       </c>
       <c r="R3" t="n">
-        <v>6212983</v>
+        <v>6213015</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +888,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Kärr med trivallövträd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,16 +908,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150442</t>
+          <t>https://artportalen.se/Sighting/137495320</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136880906</v>
+        <v>137495323</v>
       </c>
       <c r="B4" t="n">
-        <v>56963</v>
+        <v>98513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,46 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>222736</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Majbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Athyrium filix-femina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bokskog på blocklik terräng, Sk</t>
+          <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403050</v>
+        <v>402781</v>
       </c>
       <c r="R4" t="n">
-        <v>6212964</v>
+        <v>6213140</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,17 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>försvann in under en sten</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,9 +1003,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,62 +1022,54 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880906</t>
+          <t>https://artportalen.se/Sighting/137495323</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137150433</v>
+        <v>137495326</v>
       </c>
       <c r="B5" t="n">
-        <v>58194</v>
+        <v>98513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>222736</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Majbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Athyrium filix-femina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403298</v>
+        <v>402874</v>
       </c>
       <c r="R5" t="n">
-        <v>6213074</v>
+        <v>6213056</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,22 +1096,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1137,1733 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137495326</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136880893</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58903</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bokskog på blocklik terräng, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>403050</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6212964</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880893</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137150442</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58903</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>403063</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6212983</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150442</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136880906</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56963</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bokskog på blocklik terräng, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>403050</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6212964</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>försvann in under en sten</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880906</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137495339</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92821</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>403140</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6212839</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495339</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137495350</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96748</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6212887</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495350</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137495330</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96659</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>403069</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6212978</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495330</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137495364</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96659</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>403351</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6213096</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495364</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137495357</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81193</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>403312</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6212937</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495357</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137495348</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>403245</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6212891</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495348</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137150433</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>403298</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6213074</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137150433</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137495347</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>403208</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6212824</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495347</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137495352</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>403291</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6212901</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495352</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137495327</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>402942</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6213071</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Ängsädellövskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495327</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137495355</v>
+      </c>
+      <c r="B19" t="n">
+        <v>61596</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>403317</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6212914</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495355</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137495353</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106622</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>403310</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6212911</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495353</t>
         </is>
       </c>
     </row>
@@ -1149,6 +2873,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137495322</v>
+        <v>137498054</v>
       </c>
       <c r="B2" t="n">
-        <v>106622</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221157</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 39820-26 v. Koholma, Sk</t>
+          <t>Koholma Aggarp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402872</v>
+        <v>402787</v>
       </c>
       <c r="R2" t="n">
-        <v>6213052</v>
+        <v>6213174</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hålträd spillkråka Större hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Ädellövsumpskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495322</t>
+          <t>https://artportalen.se/Sighting/137498054</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137495320</v>
+        <v>137495322</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>106622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221157</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402881</v>
+        <v>402872</v>
       </c>
       <c r="R3" t="n">
-        <v>6213015</v>
+        <v>6213052</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +891,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Kärr med trivallövträd</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,16 +908,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495320</t>
+          <t>https://artportalen.se/Sighting/137495322</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137495323</v>
+        <v>137495320</v>
       </c>
       <c r="B4" t="n">
-        <v>98513</v>
+        <v>98296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222736</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Majbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Athyrium filix-femina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402781</v>
+        <v>402881</v>
       </c>
       <c r="R4" t="n">
-        <v>6213140</v>
+        <v>6213015</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Kärr med trivallövträd</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1025,13 +1025,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495323</t>
+          <t>https://artportalen.se/Sighting/137495320</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137495326</v>
+        <v>137495323</v>
       </c>
       <c r="B5" t="n">
         <v>98513</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402874</v>
+        <v>402781</v>
       </c>
       <c r="R5" t="n">
-        <v>6213056</v>
+        <v>6213140</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,6 +1122,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1137,16 +1142,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495326</t>
+          <t>https://artportalen.se/Sighting/137495323</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136880893</v>
+        <v>137495326</v>
       </c>
       <c r="B6" t="n">
-        <v>58903</v>
+        <v>98513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,46 +1159,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>222736</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Majbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Athyrium filix-femina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bokskog på blocklik terräng, Sk</t>
+          <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403050</v>
+        <v>402874</v>
       </c>
       <c r="R6" t="n">
-        <v>6212964</v>
+        <v>6213056</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,12 +1213,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,7 +1237,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,20 +1251,16 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880893</t>
+          <t>https://artportalen.se/Sighting/137495326</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137150442</v>
+        <v>136880893</v>
       </c>
       <c r="B7" t="n">
         <v>58903</v>
@@ -1287,20 +1288,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 39820-26 v. Koholma, Sk</t>
+          <t>Bokskog på blocklik terräng, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403063</v>
+        <v>403050</v>
       </c>
       <c r="R7" t="n">
-        <v>6212983</v>
+        <v>6212964</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,27 +1337,18 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,19 +1363,23 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150442</t>
+          <t>https://artportalen.se/Sighting/136880893</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136880906</v>
+        <v>137150442</v>
       </c>
       <c r="B8" t="n">
-        <v>56963</v>
+        <v>58903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,46 +1387,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bokskog på blocklik terräng, Sk</t>
+          <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403050</v>
+        <v>403063</v>
       </c>
       <c r="R8" t="n">
-        <v>6212964</v>
+        <v>6212983</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,14 +1444,19 @@
           <t>2026-09-26</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>försvann in under en sten</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1479,64 +1479,66 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880906</t>
+          <t>https://artportalen.se/Sighting/137150442</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137495339</v>
+        <v>136880906</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>56963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1101</v>
+        <v>208255</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 39820-26 v. Koholma, Sk</t>
+          <t>Bokskog på blocklik terräng, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403140</v>
+        <v>403050</v>
       </c>
       <c r="R9" t="n">
-        <v>6212839</v>
+        <v>6212964</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,44 +1562,29 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>försvann in under en sten</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1609,57 +1596,64 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495339</t>
+          <t>https://artportalen.se/Sighting/136880906</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137495350</v>
+        <v>137495339</v>
       </c>
       <c r="B10" t="n">
-        <v>96748</v>
+        <v>92821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>1101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403271</v>
+        <v>403140</v>
       </c>
       <c r="R10" t="n">
-        <v>6212887</v>
+        <v>6212839</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,17 +1692,28 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1724,16 +1729,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495350</t>
+          <t>https://artportalen.se/Sighting/137495339</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137495330</v>
+        <v>137495350</v>
       </c>
       <c r="B11" t="n">
-        <v>96659</v>
+        <v>96748</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,13 +1770,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403069</v>
+        <v>403271</v>
       </c>
       <c r="R11" t="n">
-        <v>6212978</v>
+        <v>6212887</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,13 +1841,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495330</t>
+          <t>https://artportalen.se/Sighting/137495350</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137495364</v>
+        <v>137495330</v>
       </c>
       <c r="B12" t="n">
         <v>96659</v>
@@ -1877,13 +1882,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403351</v>
+        <v>403069</v>
       </c>
       <c r="R12" t="n">
-        <v>6213096</v>
+        <v>6212978</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,16 +1953,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495364</t>
+          <t>https://artportalen.se/Sighting/137495330</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137495357</v>
+        <v>137495364</v>
       </c>
       <c r="B13" t="n">
-        <v>81193</v>
+        <v>96659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,21 +1970,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6444</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1989,13 +1994,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403312</v>
+        <v>403351</v>
       </c>
       <c r="R13" t="n">
-        <v>6212937</v>
+        <v>6213096</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2024,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,16 +2065,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495357</t>
+          <t>https://artportalen.se/Sighting/137495364</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137495348</v>
+        <v>137495357</v>
       </c>
       <c r="B14" t="n">
-        <v>58032</v>
+        <v>81193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,35 +2082,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6444</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403245</v>
+        <v>403312</v>
       </c>
       <c r="R14" t="n">
-        <v>6212891</v>
+        <v>6212937</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2137,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,33 +2177,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495348</t>
+          <t>https://artportalen.se/Sighting/137495357</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137150433</v>
+        <v>137495348</v>
       </c>
       <c r="B15" t="n">
-        <v>58194</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2207,21 +2211,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403298</v>
+        <v>403245</v>
       </c>
       <c r="R15" t="n">
-        <v>6213074</v>
+        <v>6212891</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,22 +2249,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,16 +2290,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150433</t>
+          <t>https://artportalen.se/Sighting/137495348</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137495347</v>
+        <v>137498061</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>58471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,41 +2307,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103020</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 39820-26 v. Koholma, Sk</t>
+          <t>Koholma Aggarp, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403208</v>
+        <v>403122</v>
       </c>
       <c r="R16" t="n">
-        <v>6212824</v>
+        <v>6212843</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,24 +2395,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495347</t>
+          <t>https://artportalen.se/Sighting/137498061</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137495352</v>
+        <v>137150433</v>
       </c>
       <c r="B17" t="n">
         <v>58194</v>
@@ -2441,7 +2442,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2450,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403291</v>
+        <v>403298</v>
       </c>
       <c r="R17" t="n">
-        <v>6212901</v>
+        <v>6213074</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2480,22 +2481,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,51 +2522,55 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495352</t>
+          <t>https://artportalen.se/Sighting/137150433</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137495327</v>
+        <v>137495347</v>
       </c>
       <c r="B18" t="n">
-        <v>58658</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103041</v>
+        <v>103020</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>402942</v>
+        <v>403208</v>
       </c>
       <c r="R18" t="n">
-        <v>6213071</v>
+        <v>6212824</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2597,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,11 +2623,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Ängsädellövskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2638,16 +2638,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495327</t>
+          <t>https://artportalen.se/Sighting/137495347</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137495355</v>
+        <v>137495352</v>
       </c>
       <c r="B19" t="n">
-        <v>61596</v>
+        <v>58194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106670</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2672,20 +2672,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 39820-26 v. Koholma, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403317</v>
+        <v>403291</v>
       </c>
       <c r="R19" t="n">
-        <v>6212914</v>
+        <v>6212901</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2714,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2724,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,7 +2737,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2751,51 +2754,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495355</t>
+          <t>https://artportalen.se/Sighting/137495352</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137495353</v>
+        <v>137498058</v>
       </c>
       <c r="B20" t="n">
-        <v>106622</v>
+        <v>58194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221157</v>
+        <v>103020</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 39820-26 v. Koholma, Sk</t>
+          <t>Koholma Aggarp, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403310</v>
+        <v>403130</v>
       </c>
       <c r="R20" t="n">
-        <v>6212911</v>
+        <v>6212959</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2827,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2840,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Uv</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,16 +2860,708 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137498058</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137498062</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Koholma Aggarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>403261</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6212930</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137498062</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137498063</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Koholma Aggarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>403300</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6212909</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137498063</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137495327</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>402942</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6213071</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Ängsädellövskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495327</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137498056</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Koholma Aggarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>403129</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6212956</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137498056</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137495355</v>
+      </c>
+      <c r="B25" t="n">
+        <v>61596</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>403317</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6212914</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495355</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137495353</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106622</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>403310</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6212911</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137495353</t>
         </is>
@@ -2888,6 +3588,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4865-2022 artfynd.xlsx
+++ b/artfynd/S 4865-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137498054</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137495322</v>
       </c>
       <c r="B3" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137495320</v>
       </c>
       <c r="B4" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>137495323</v>
       </c>
       <c r="B5" t="n">
-        <v>98513</v>
+        <v>98517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137495326</v>
       </c>
       <c r="B6" t="n">
-        <v>98513</v>
+        <v>98517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>137150442</v>
       </c>
       <c r="B8" t="n">
-        <v>58903</v>
+        <v>58906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137495339</v>
       </c>
       <c r="B10" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137495350</v>
       </c>
       <c r="B11" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137495330</v>
       </c>
       <c r="B12" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>137495364</v>
       </c>
       <c r="B13" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137495357</v>
       </c>
       <c r="B14" t="n">
-        <v>81193</v>
+        <v>81197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137495348</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137498061</v>
       </c>
       <c r="B16" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137150433</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>137495347</v>
       </c>
       <c r="B18" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137495352</v>
       </c>
       <c r="B19" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>137498058</v>
       </c>
       <c r="B20" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137498062</v>
       </c>
       <c r="B21" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>137498063</v>
       </c>
       <c r="B22" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>137495327</v>
       </c>
       <c r="B23" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>137498056</v>
       </c>
       <c r="B24" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>137495355</v>
       </c>
       <c r="B25" t="n">
-        <v>61596</v>
+        <v>61600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>137495353</v>
       </c>
       <c r="B26" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
